--- a/Java_Selenium_Batch_1_Capstone_Project.xlsx
+++ b/Java_Selenium_Batch_1_Capstone_Project.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7c05477d0ad59ef/Desktop/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{80320C52-5062-4567-A899-5F3D79A0AD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="8_{80320C52-5062-4567-A899-5F3D79A0AD1A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EAD07335-B099-4EA2-B167-9507F92E34E6}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{124B4E3D-77E1-470B-83A3-A7978E63010D}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>S No</t>
   </si>
@@ -169,6 +169,9 @@
   </si>
   <si>
     <t>PULAKUNTA SARITHA</t>
+  </si>
+  <si>
+    <t>Capstone_Project_Git_Link</t>
   </si>
 </sst>
 </file>
@@ -616,15 +619,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9C56D031-3353-4F8C-88A6-A34A4269BBE8}">
-  <dimension ref="A1:C43"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
     <col min="2" max="2" width="14.90625" customWidth="1"/>
     <col min="3" max="3" width="37.54296875" customWidth="1"/>
+    <col min="4" max="4" width="25.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -634,8 +638,11 @@
       <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="D1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -646,7 +653,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -657,7 +664,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -668,7 +675,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -679,7 +686,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -690,7 +697,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -701,7 +708,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="3">
         <v>8</v>
       </c>
@@ -712,7 +719,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="3">
         <v>9</v>
       </c>
@@ -723,7 +730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="3">
         <v>10</v>
       </c>
@@ -734,7 +741,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="3">
         <v>11</v>
       </c>
@@ -745,7 +752,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="3">
         <v>13</v>
       </c>
@@ -756,7 +763,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="3">
         <v>14</v>
       </c>
@@ -767,7 +774,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="3">
         <v>15</v>
       </c>
@@ -778,7 +785,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="3">
         <v>16</v>
       </c>
@@ -789,7 +796,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="3">
         <v>17</v>
       </c>
